--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T08:45:50+00:00</t>
+    <t>2026-09-14T09:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T09:32:54+00:00</t>
+    <t>2026-09-15T09:11:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T09:11:17+00:00</t>
+    <t>2026-09-16T09:03:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:03:59+00:00</t>
+    <t>2026-09-18T08:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:45:46+00:00</t>
+    <t>2026-09-19T08:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-19T08:31:43+00:00</t>
+    <t>2026-09-20T09:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T09:02:38+00:00</t>
+    <t>2026-09-21T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T09:33:49+00:00</t>
+    <t>2026-09-22T09:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T09:02:23+00:00</t>
+    <t>2026-09-23T09:05:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:05:06+00:00</t>
+    <t>2026-09-26T09:04:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-26T09:04:06+00:00</t>
+    <t>2026-09-27T09:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-27T09:48:22+00:00</t>
+    <t>2026-09-28T10:08:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:08:08+00:00</t>
+    <t>2026-09-28T10:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:29:09+00:00</t>
+    <t>2026-09-29T10:23:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:23:21+00:00</t>
+    <t>2026-09-30T10:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:15:24+00:00</t>
+    <t>2026-10-01T10:44:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T10:44:11+00:00</t>
+    <t>2026-10-03T09:39:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-03T09:39:13+00:00</t>
+    <t>2026-10-04T10:24:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-04T10:24:59+00:00</t>
+    <t>2026-10-05T11:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-05T11:08:35+00:00</t>
+    <t>2026-10-06T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -31,10 +31,10 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:2.16.840.1.113883.6.347 (use: usual, )</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-cim11-mms (use: secondary, )</t>
+    <t>OID:2.16.840.1.113883.6.347 (use: usual)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/#terminologie-cim11-mms (use: secondary)</t>
   </si>
   <si>
     <t>Version</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T11:03:00+00:00</t>
+    <t>2026-10-07T10:51:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T10:51:41+00:00</t>
+    <t>2026-10-08T11:09:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T11:09:48+00:00</t>
+    <t>2026-10-09T11:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T11:08:13+00:00</t>
+    <t>2026-10-10T10:26:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-10T10:26:06+00:00</t>
+    <t>2026-10-11T10:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T10:34:50+00:00</t>
+    <t>2026-10-12T11:38:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T11:38:18+00:00</t>
+    <t>2026-10-13T11:24:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T11:24:48+00:00</t>
+    <t>2026-10-14T09:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T09:16:31+00:00</t>
+    <t>2026-10-16T08:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:44:55+00:00</t>
+    <t>2026-10-17T08:16:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T08:16:30+00:00</t>
+    <t>2026-10-18T08:33:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:33:19+00:00</t>
+    <t>2026-10-19T09:34:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T09:34:29+00:00</t>
+    <t>2026-10-21T09:08:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:08:03+00:00</t>
+    <t>2026-10-22T09:10:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:10:10+00:00</t>
+    <t>2026-10-23T09:04:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:04:39+00:00</t>
+    <t>2026-10-24T08:37:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-24T08:37:27+00:00</t>
+    <t>2026-10-25T08:56:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-25T08:56:52+00:00</t>
+    <t>2026-10-26T09:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T09:38:46+00:00</t>
+    <t>2026-10-27T09:35:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T09:35:46+00:00</t>
+    <t>2026-10-28T10:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:20:37+00:00</t>
+    <t>2026-10-29T10:44:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:44:18+00:00</t>
+    <t>2026-10-30T10:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/main/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T10:44:55+00:00</t>
+    <t>2026-10-31T10:10:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
